--- a/tests/load-testing/load_test_report.xlsx
+++ b/tests/load-testing/load_test_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Load Test Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Individual Request Logs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Test Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Individual Request Logs" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/tests/load-testing/load_test_report.xlsx
+++ b/tests/load-testing/load_test_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Test Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Individual Request Logs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Load Test Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Individual Request Logs" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/tests/load-testing/load_test_report.xlsx
+++ b/tests/load-testing/load_test_report.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -116,6 +116,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,7 +490,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -523,7 +527,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5 seconds</t>
+          <t>5.0 seconds</t>
         </is>
       </c>
     </row>
@@ -534,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +549,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>0.0 req/sec</t>
+          <t>26.4 req/sec</t>
         </is>
       </c>
     </row>
@@ -557,7 +561,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>132 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -589,7 +593,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>93 ms</t>
         </is>
       </c>
     </row>
@@ -601,7 +605,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>347 ms</t>
         </is>
       </c>
     </row>
@@ -613,7 +617,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>947 ms</t>
         </is>
       </c>
     </row>
@@ -625,7 +629,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>288 ms</t>
         </is>
       </c>
     </row>
@@ -637,7 +641,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>628 ms</t>
         </is>
       </c>
     </row>
@@ -649,7 +653,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>786 ms</t>
         </is>
       </c>
     </row>
@@ -661,7 +665,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>896 ms</t>
         </is>
       </c>
     </row>
@@ -679,12 +683,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -722,6 +726,3702 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>0.042s</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>526</v>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>0.059s</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>311</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>0.072s</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>598</v>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>0.085s</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>656</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>0.099s</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>0.112s</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0.126s</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>630</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>0.139s</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>0.153s</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>418</v>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>0.166s</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>0.322s</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>645</v>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>0.332s</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>628</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>0.380s</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>598</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>0.567s</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>0.577s</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>0.578s</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>0.581s</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>582</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>0.681s</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>0.752s</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>211</v>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>0.766s</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>305</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0021</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>0.868s</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0022</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>0.872s</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0023</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>0.881s</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0024</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>0.972s</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0025</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>0.974s</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0026</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>0.976s</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0027</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>0.976s</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0028</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>0.977s</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>490</v>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0029</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>0.989s</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>577</v>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0030</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>1.083s</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>581</v>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0031</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>1.091s</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>572</v>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0032</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>1.168s</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>505</v>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0033</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>1.174s</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>501</v>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0034</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>1.174s</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>893</v>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0035</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>1.179s</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>495</v>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0036</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>1.186s</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>947</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0037</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>1.268s</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>896</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0038</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>1.477s</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0039</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>1.577s</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>389</v>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0040</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>1.674s</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0041</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>1.675s</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>292</v>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0042</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>1.683s</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>773</v>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0043</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>1.685s</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0044</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>1.685s</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>779</v>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0045</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>1.872s</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>292</v>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0046</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>1.973s</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0047</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>1.977s</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0048</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>1.977s</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0049</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>1.981s</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0050</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2.078s</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0051</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>2.144s</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0052</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2.175s</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0053</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2.175s</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0054</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2.275s</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0055</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2.277s</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>483</v>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0056</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>2.277s</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0057</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2.279s</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0058</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>2.279s</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0059</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>2.279s</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0060</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>2.467s</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0061</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>2.472s</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0062</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>2.475s</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0063</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2.575s</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>387</v>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0064</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2.578s</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0065</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2.578s</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0066</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>2.579s</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0067</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>2.581s</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0068</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>2.586s</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0069</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>2.680s</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0070</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>2.684s</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0071</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>2.770s</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0072</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2.777s</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0073</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>2.777s</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0074</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>2.875s</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0075</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>2.878s</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0076</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>2.880s</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>472</v>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0077</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>2.885s</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0078</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>2.974s</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0079</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>2.974s</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>477</v>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0080</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>2.974s</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0081</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>2.976s</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0082</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>2.980s</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>880</v>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0083</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>3.077s</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>781</v>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0084</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>3.169s</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>799</v>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0085</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>3.173s</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>797</v>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0086</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>3.180s</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>786</v>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0087</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>3.359s</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0088</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>3.359s</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0089</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>3.360s</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0090</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>3.363s</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0091</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>3.461s</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0092</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>3.558s</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0093</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>3.558s</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0094</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>3.558s</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0095</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>3.670s</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0096</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>3.670s</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>292</v>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0097</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>3.670s</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0098</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>3.756s</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0099</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>3.757s</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0100</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>3.866s</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0101</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>3.869s</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0102</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>3.871s</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0103</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>3.871s</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0104</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>3.972s</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0105</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>3.973s</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0106</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>3.975s</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0107</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>3.977s</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0108</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>3.979s</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0109</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>3.981s</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0110</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>4.066s</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0111</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>4.073s</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>497</v>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0112</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>4.075s</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0113</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>4.079s</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0114</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>4.183s</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0115</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>4.266s</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0116</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>4.271s</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0117</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>4.275s</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0118</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>4.279s</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>584</v>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0119</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>4.279s</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0120</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>4.279s</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0121</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>4.378s</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0122</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>4.474s</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0123</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>4.475s</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0124</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>4.477s</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0125</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>4.477s</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0126</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>4.479s</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>193</v>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0127</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>4.582s</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0128</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>4.585s</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0129</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>4.670s</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0130</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>4.675s</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>193</v>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0131</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>4.676s</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0132</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>4.676s</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/load-testing/load_test_report.xlsx
+++ b/tests/load-testing/load_test_report.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -116,6 +116,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,7 +490,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -523,7 +527,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5 seconds</t>
+          <t>5.0 seconds</t>
         </is>
       </c>
     </row>
@@ -534,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +549,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>0.0 req/sec</t>
+          <t>23.6 req/sec</t>
         </is>
       </c>
     </row>
@@ -557,7 +561,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>118 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -589,7 +593,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>93 ms</t>
         </is>
       </c>
     </row>
@@ -601,7 +605,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>382 ms</t>
         </is>
       </c>
     </row>
@@ -613,7 +617,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>1263 ms</t>
         </is>
       </c>
     </row>
@@ -625,7 +629,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>297 ms</t>
         </is>
       </c>
     </row>
@@ -637,7 +641,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>576 ms</t>
         </is>
       </c>
     </row>
@@ -649,7 +653,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>884 ms</t>
         </is>
       </c>
     </row>
@@ -661,7 +665,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>0 ms</t>
+          <t>1142 ms</t>
         </is>
       </c>
     </row>
@@ -679,12 +683,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -722,6 +726,3310 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>0.067s</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1263</v>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>0.090s</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>1142</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>0.108s</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>536</v>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>0.126s</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>921</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>0.145s</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>299</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>0.163s</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1072</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0.182s</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>754</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>0.200s</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>838</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>0.218s</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>514</v>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>0.236s</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>1104</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>0.454s</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>884</v>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>0.655s</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>0.742s</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>0.947s</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>0.947s</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>383</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>1.049s</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>1.049s</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>1.051s</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>1.058s</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>1.242s</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>707</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0021</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>1.246s</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0022</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>1.334s</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>389</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0023</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>1.340s</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0024</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>1.342s</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0025</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>1.342s</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>493</v>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0026</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>1.342s</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0027</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>1.345s</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0028</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>1.349s</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>581</v>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0029</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>1.351s</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>576</v>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0030</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>1.537s</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>194</v>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0031</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>1.639s</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0032</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>1.645s</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0033</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>1.733s</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0034</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>1.734s</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0035</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>1.735s</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0036</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>1.742s</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0037</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>1.838s</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0038</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>1.846s</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0039</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>1.938s</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0040</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>1.938s</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0041</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>1.941s</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0042</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>1.946s</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0043</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>1.960s</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0044</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2.031s</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0045</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2.037s</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0046</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2.043s</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0047</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2.133s</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>695</v>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0048</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2.234s</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>393</v>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0049</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2.236s</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>391</v>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0050</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2.241s</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0051</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>2.244s</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0052</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2.252s</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>475</v>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0053</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2.259s</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0054</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2.261s</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>572</v>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0055</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2.332s</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>518</v>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0056</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>2.433s</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>395</v>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0057</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2.637s</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0058</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>2.638s</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0059</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>2.640s</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>383</v>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0060</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>2.640s</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0061</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>2.641s</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0062</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>2.738s</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>297</v>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0063</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2.840s</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0064</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2.840s</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0065</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2.843s</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0066</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>2.860s</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0067</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>2.932s</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0068</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>2.932s</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0069</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>2.944s</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0070</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>3.033s</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0071</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>3.033s</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0072</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>3.045s</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0073</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>3.137s</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>292</v>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0074</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>3.141s</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0075</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>3.164s</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0076</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>3.164s</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0077</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>3.236s</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>383</v>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0078</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>3.237s</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0079</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>3.240s</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0080</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>3.242s</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>483</v>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0081</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>3.246s</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>486</v>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0082</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>3.332s</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0083</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>3.440s</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0084</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>3.446s</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0085</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>3.545s</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0086</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>3.545s</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0087</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>3.632s</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>299</v>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0088</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>3.633s</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0089</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>3.633s</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>298</v>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0090</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>3.732s</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>393</v>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0091</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>3.733s</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>301</v>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0092</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>3.736s</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>297</v>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0093</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>3.742s</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>382</v>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0094</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>3.742s</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>383</v>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0095</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>3.746s</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>396</v>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0096</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>3.835s</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>495</v>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0097</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>3.938s</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>387</v>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0098</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>3.941s</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>403</v>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0099</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>3.942s</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0100</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>4.045s</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0101</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>4.045s</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0102</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>4.135s</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0103</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>4.135s</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0104</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>4.136s</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0105</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>4.145s</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0106</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>4.153s</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0107</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>4.336s</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0108</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>4.340s</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0109</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>4.340s</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0110</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>4.341s</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0111</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>4.343s</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0112</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>4.355s</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0113</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>4.436s</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0114</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>4.536s</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0115</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>4.638s</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0116</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>4.638s</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0117</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>4.639s</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>REQ_0118</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>4.644s</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/load-testing/load_test_report.xlsx
+++ b/tests/load-testing/load_test_report.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -549,7 +549,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>23.6 req/sec</t>
+          <t>23.2 req/sec</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>118 (100.0%)</t>
+          <t>116 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>93 ms</t>
+          <t>137 ms</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>382 ms</t>
+          <t>392 ms</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>1263 ms</t>
+          <t>1055 ms</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>297 ms</t>
+          <t>349 ms</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>576 ms</t>
+          <t>657 ms</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>884 ms</t>
+          <t>872 ms</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>1142 ms</t>
+          <t>997 ms</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0.067s</t>
+          <t>0.054s</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -746,7 +746,7 @@
         <v>200</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1263</v>
+        <v>929</v>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0.090s</t>
+          <t>0.076s</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -774,7 +774,7 @@
         <v>200</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1142</v>
+        <v>606</v>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>0.108s</t>
+          <t>0.095s</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -802,7 +802,7 @@
         <v>200</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>536</v>
+        <v>997</v>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>0.126s</t>
+          <t>0.113s</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -830,7 +830,7 @@
         <v>200</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>921</v>
+        <v>971</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0.145s</t>
+          <t>0.131s</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -858,7 +858,7 @@
         <v>200</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0.163s</t>
+          <t>0.149s</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -886,7 +886,7 @@
         <v>200</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1072</v>
+        <v>601</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.182s</t>
+          <t>0.167s</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -914,7 +914,7 @@
         <v>200</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>754</v>
+        <v>821</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>0.200s</t>
+          <t>0.185s</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -942,7 +942,7 @@
         <v>200</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>838</v>
+        <v>1055</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>0.218s</t>
+          <t>0.203s</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -970,7 +970,7 @@
         <v>200</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>514</v>
+        <v>872</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0.236s</t>
+          <t>0.221s</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -998,7 +998,7 @@
         <v>200</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1104</v>
+        <v>769</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>0.454s</t>
+          <t>0.458s</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1026,7 +1026,7 @@
         <v>200</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>884</v>
+        <v>924</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>0.655s</t>
+          <t>0.693s</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1054,7 +1054,7 @@
         <v>200</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>281</v>
+        <v>184</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>0.742s</t>
+          <t>0.761s</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>200</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>0.947s</t>
+          <t>0.888s</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1110,7 +1110,7 @@
         <v>200</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>93</v>
+        <v>447</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>0.947s</t>
+          <t>0.994s</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>200</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>383</v>
+        <v>186</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>1.049s</t>
+          <t>1.000s</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1166,7 +1166,7 @@
         <v>200</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>285</v>
+        <v>175</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>1.049s</t>
+          <t>1.001s</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1194,7 +1194,7 @@
         <v>200</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>1.051s</t>
+          <t>1.025s</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1222,7 +1222,7 @@
         <v>200</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>1.058s</t>
+          <t>1.086s</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1250,7 +1250,7 @@
         <v>200</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>1.242s</t>
+          <t>1.095s</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1278,7 +1278,7 @@
         <v>200</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>707</v>
+        <v>243</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>1.246s</t>
+          <t>1.103s</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1306,7 +1306,7 @@
         <v>200</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>1.334s</t>
+          <t>1.149s</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1334,7 +1334,7 @@
         <v>200</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>389</v>
+        <v>288</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>1.340s</t>
+          <t>1.186s</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1362,7 +1362,7 @@
         <v>200</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>1.342s</t>
+          <t>1.191s</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1390,7 +1390,7 @@
         <v>200</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>1.342s</t>
+          <t>1.251s</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1418,7 +1418,7 @@
         <v>200</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>493</v>
+        <v>228</v>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>1.342s</t>
+          <t>1.291s</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1446,7 +1446,7 @@
         <v>200</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>1.345s</t>
+          <t>1.301s</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1474,7 +1474,7 @@
         <v>200</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>282</v>
+        <v>455</v>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>1.349s</t>
+          <t>1.346s</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -1502,7 +1502,7 @@
         <v>200</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>581</v>
+        <v>203</v>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>1.351s</t>
+          <t>1.350s</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -1530,7 +1530,7 @@
         <v>200</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>576</v>
+        <v>192</v>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>1.537s</t>
+          <t>1.391s</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>200</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>194</v>
+        <v>349</v>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>1.639s</t>
+          <t>1.393s</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -1586,7 +1586,7 @@
         <v>200</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>188</v>
+        <v>387</v>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>1.645s</t>
+          <t>1.448s</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -1614,7 +1614,7 @@
         <v>200</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>281</v>
+        <v>393</v>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>1.733s</t>
+          <t>1.490s</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -1642,7 +1642,7 @@
         <v>200</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>1.734s</t>
+          <t>1.494s</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -1670,7 +1670,7 @@
         <v>200</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>1.735s</t>
+          <t>1.547s</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -1698,7 +1698,7 @@
         <v>200</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>296</v>
+        <v>693</v>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>1.742s</t>
+          <t>1.553s</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>200</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>283</v>
+        <v>696</v>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>1.838s</t>
+          <t>1.555s</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -1754,7 +1754,7 @@
         <v>200</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>285</v>
+        <v>498</v>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>1.846s</t>
+          <t>1.560s</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -1782,7 +1782,7 @@
         <v>200</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>404</v>
+        <v>584</v>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>1.938s</t>
+          <t>1.750s</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -1810,7 +1810,7 @@
         <v>200</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>286</v>
+        <v>202</v>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>1.938s</t>
+          <t>1.767s</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -1838,7 +1838,7 @@
         <v>200</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>1.941s</t>
+          <t>1.768s</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -1866,7 +1866,7 @@
         <v>200</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>1.946s</t>
+          <t>1.768s</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>200</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>1.960s</t>
+          <t>1.791s</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -1922,7 +1922,7 @@
         <v>200</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>288</v>
+        <v>657</v>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2.031s</t>
+          <t>1.852s</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -1950,7 +1950,7 @@
         <v>200</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>202</v>
+        <v>589</v>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2.037s</t>
+          <t>1.953s</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -1978,7 +1978,7 @@
         <v>200</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2.043s</t>
+          <t>1.964s</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -2006,7 +2006,7 @@
         <v>200</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>380</v>
+        <v>476</v>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2.133s</t>
+          <t>2.054s</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -2034,7 +2034,7 @@
         <v>200</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>695</v>
+        <v>386</v>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2.234s</t>
+          <t>2.054s</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -2062,7 +2062,7 @@
         <v>200</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>393</v>
+        <v>283</v>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2.236s</t>
+          <t>2.065s</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -2090,7 +2090,7 @@
         <v>200</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2.241s</t>
+          <t>2.155s</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -2118,7 +2118,7 @@
         <v>200</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>2.244s</t>
+          <t>2.251s</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -2146,7 +2146,7 @@
         <v>200</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>385</v>
+        <v>293</v>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2.252s</t>
+          <t>2.259s</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -2174,7 +2174,7 @@
         <v>200</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>475</v>
+        <v>286</v>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>200</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2.261s</t>
+          <t>2.348s</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -2230,7 +2230,7 @@
         <v>200</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>572</v>
+        <v>308</v>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2.332s</t>
+          <t>2.451s</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -2258,7 +2258,7 @@
         <v>200</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>518</v>
+        <v>309</v>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2.433s</t>
+          <t>2.451s</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -2286,7 +2286,7 @@
         <v>200</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>395</v>
+        <v>307</v>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2.637s</t>
+          <t>2.452s</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -2314,7 +2314,7 @@
         <v>200</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>296</v>
+        <v>498</v>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2.638s</t>
+          <t>2.458s</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -2342,7 +2342,7 @@
         <v>200</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>2.640s</t>
+          <t>2.458s</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -2370,7 +2370,7 @@
         <v>200</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2.640s</t>
+          <t>2.547s</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -2398,7 +2398,7 @@
         <v>200</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>381</v>
+        <v>295</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>2.641s</t>
+          <t>2.555s</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -2426,7 +2426,7 @@
         <v>200</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2.738s</t>
+          <t>2.555s</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -2454,7 +2454,7 @@
         <v>200</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>2.840s</t>
+          <t>2.668s</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -2482,7 +2482,7 @@
         <v>200</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2.840s</t>
+          <t>2.668s</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -2510,7 +2510,7 @@
         <v>200</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>2.843s</t>
+          <t>2.771s</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -2538,7 +2538,7 @@
         <v>200</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>309</v>
+        <v>379</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>2.860s</t>
+          <t>2.771s</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -2566,7 +2566,7 @@
         <v>200</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>293</v>
+        <v>464</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>2.932s</t>
+          <t>2.851s</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
@@ -2594,7 +2594,7 @@
         <v>200</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>294</v>
+        <v>398</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2.932s</t>
+          <t>2.853s</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -2622,7 +2622,7 @@
         <v>200</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>293</v>
+        <v>394</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>2.944s</t>
+          <t>2.853s</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
@@ -2650,7 +2650,7 @@
         <v>200</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>285</v>
+        <v>395</v>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>3.033s</t>
+          <t>2.864s</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -2678,7 +2678,7 @@
         <v>200</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>289</v>
+        <v>483</v>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>3.033s</t>
+          <t>2.950s</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -2706,7 +2706,7 @@
         <v>200</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>198</v>
+        <v>493</v>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>3.045s</t>
+          <t>2.962s</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -2734,7 +2734,7 @@
         <v>200</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>189</v>
+        <v>379</v>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>3.137s</t>
+          <t>2.962s</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -2762,7 +2762,7 @@
         <v>200</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>292</v>
+        <v>386</v>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>3.141s</t>
+          <t>2.973s</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -2790,7 +2790,7 @@
         <v>200</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>294</v>
+        <v>686</v>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>3.164s</t>
+          <t>3.161s</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -2818,7 +2818,7 @@
         <v>200</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>370</v>
+        <v>287</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>3.164s</t>
+          <t>3.247s</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -2846,7 +2846,7 @@
         <v>200</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>3.236s</t>
+          <t>3.258s</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
@@ -2874,7 +2874,7 @@
         <v>200</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>383</v>
+        <v>281</v>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>3.237s</t>
+          <t>3.259s</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -2902,7 +2902,7 @@
         <v>200</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>3.240s</t>
+          <t>3.260s</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -2930,7 +2930,7 @@
         <v>200</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>3.242s</t>
+          <t>3.352s</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -2958,7 +2958,7 @@
         <v>200</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>483</v>
+        <v>309</v>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>3.246s</t>
+          <t>3.358s</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -2986,7 +2986,7 @@
         <v>200</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>486</v>
+        <v>303</v>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>3.332s</t>
+          <t>3.359s</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -3014,7 +3014,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>3.440s</t>
+          <t>3.454s</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -3042,7 +3042,7 @@
         <v>200</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>3.446s</t>
+          <t>3.459s</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -3070,7 +3070,7 @@
         <v>200</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>3.545s</t>
+          <t>3.549s</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -3098,7 +3098,7 @@
         <v>200</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>279</v>
+        <v>400</v>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>3.545s</t>
+          <t>3.652s</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -3126,7 +3126,7 @@
         <v>200</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>190</v>
+        <v>496</v>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>3.632s</t>
+          <t>3.653s</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -3154,7 +3154,7 @@
         <v>200</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>3.633s</t>
+          <t>3.657s</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -3182,7 +3182,7 @@
         <v>200</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>294</v>
+        <v>383</v>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>3.633s</t>
+          <t>3.670s</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -3210,7 +3210,7 @@
         <v>200</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>298</v>
+        <v>373</v>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>3.732s</t>
+          <t>3.670s</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -3238,7 +3238,7 @@
         <v>200</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>393</v>
+        <v>480</v>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>3.733s</t>
+          <t>3.672s</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
@@ -3266,7 +3266,7 @@
         <v>200</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>301</v>
+        <v>570</v>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>3.736s</t>
+          <t>3.672s</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -3294,7 +3294,7 @@
         <v>200</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>297</v>
+        <v>582</v>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>3.742s</t>
+          <t>3.767s</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -3322,7 +3322,7 @@
         <v>200</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>3.742s</t>
+          <t>3.775s</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -3350,7 +3350,7 @@
         <v>200</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>3.746s</t>
+          <t>3.960s</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
@@ -3378,7 +3378,7 @@
         <v>200</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>396</v>
+        <v>288</v>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>3.835s</t>
+          <t>3.960s</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -3406,7 +3406,7 @@
         <v>200</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>495</v>
+        <v>298</v>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>3.938s</t>
+          <t>4.051s</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
@@ -3434,7 +3434,7 @@
         <v>200</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>3.941s</t>
+          <t>4.054s</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -3462,7 +3462,7 @@
         <v>200</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>3.942s</t>
+          <t>4.159s</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
@@ -3490,7 +3490,7 @@
         <v>200</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>191</v>
+        <v>384</v>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>4.045s</t>
+          <t>4.161s</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
@@ -3518,7 +3518,7 @@
         <v>200</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>283</v>
+        <v>187</v>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>4.045s</t>
+          <t>4.161s</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
@@ -3546,7 +3546,7 @@
         <v>200</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>4.135s</t>
+          <t>4.166s</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
@@ -3574,7 +3574,7 @@
         <v>200</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>4.135s</t>
+          <t>4.253s</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
@@ -3602,7 +3602,7 @@
         <v>200</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>197</v>
+        <v>292</v>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>4.136s</t>
+          <t>4.259s</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
@@ -3630,7 +3630,7 @@
         <v>200</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>500</v>
+        <v>289</v>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>4.145s</t>
+          <t>4.265s</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -3658,7 +3658,7 @@
         <v>200</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>4.153s</t>
+          <t>4.270s</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
@@ -3686,7 +3686,7 @@
         <v>200</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>480</v>
+        <v>372</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>4.336s</t>
+          <t>4.358s</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -3714,7 +3714,7 @@
         <v>200</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>500</v>
+        <v>377</v>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>4.340s</t>
+          <t>4.454s</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
@@ -3742,7 +3742,7 @@
         <v>200</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>4.340s</t>
+          <t>4.455s</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
@@ -3770,7 +3770,7 @@
         <v>200</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>4.341s</t>
+          <t>4.458s</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
@@ -3798,7 +3798,7 @@
         <v>200</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>4.343s</t>
+          <t>4.460s</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>4.355s</t>
+          <t>4.554s</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
@@ -3854,7 +3854,7 @@
         <v>200</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>4.436s</t>
+          <t>4.556s</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
@@ -3882,7 +3882,7 @@
         <v>200</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>196</v>
+        <v>288</v>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>4.536s</t>
+          <t>4.559s</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
@@ -3910,7 +3910,7 @@
         <v>200</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>4.638s</t>
+          <t>4.646s</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -3938,7 +3938,7 @@
         <v>200</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>4.638s</t>
+          <t>4.653s</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
@@ -3966,65 +3966,9 @@
         <v>200</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>197</v>
+        <v>289</v>
       </c>
       <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>REQ_0117</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>4.639s</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>287</v>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>REQ_0118</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>4.644s</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>https://privacyshield-backend-awon.onrender.com/health/readiness</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>287</v>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
